--- a/Heuristic/Experiments/Results/Deterministic results, samlet.xlsx
+++ b/Heuristic/Experiments/Results/Deterministic results, samlet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\Heuristic\Experiments\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63402D59-CDFB-4650-927D-5E8B7813FC1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E31C7D79-43EE-49D4-9176-C710F033B596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="11260" firstSheet="2" activeTab="10" xr2:uid="{3A184787-BD53-4D94-B163-FCD1CFFF27BA}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="11260" activeTab="6" xr2:uid="{3A184787-BD53-4D94-B163-FCD1CFFF27BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Base case" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2729" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2546" uniqueCount="152">
   <si>
     <t>run</t>
   </si>
@@ -249,28 +249,10 @@
     <t>legs:</t>
   </si>
   <si>
-    <t>dt=92.0</t>
-  </si>
-  <si>
-    <t>dt=722.0</t>
-  </si>
-  <si>
     <t>dt=153.0</t>
   </si>
   <si>
-    <t>dt=611.0</t>
-  </si>
-  <si>
-    <t>dt=148.0</t>
-  </si>
-  <si>
-    <t>dt=216.0</t>
-  </si>
-  <si>
     <t>q=1</t>
-  </si>
-  <si>
-    <t>dt=106.0</t>
   </si>
   <si>
     <t>dt=463.0</t>
@@ -307,12 +289,6 @@
   </si>
   <si>
     <t>dt=145.0</t>
-  </si>
-  <si>
-    <t>Average</t>
-  </si>
-  <si>
-    <t>STD</t>
   </si>
   <si>
     <t>dt=201.0</t>
@@ -530,12 +506,18 @@
   <si>
     <t>dt=104.0</t>
   </si>
+  <si>
+    <t>scenario</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -550,6 +532,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF202020"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -574,8 +562,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -615,7 +605,7 @@
           <cx:tx>
             <cx:txData>
               <cx:f>_xlchart.v1.0</cx:f>
-              <cx:v>best_obj</cx:v>
+              <cx:v>run</cx:v>
             </cx:txData>
           </cx:tx>
           <cx:dataId val="0"/>
@@ -628,7 +618,7 @@
           <cx:tx>
             <cx:txData>
               <cx:f>_xlchart.v1.2</cx:f>
-              <cx:v>best_profit</cx:v>
+              <cx:v>best_obj</cx:v>
             </cx:txData>
           </cx:tx>
           <cx:dataId val="1"/>
@@ -1608,7 +1598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7BFF44A-2695-490E-A9CD-62E25082CEF5}">
-  <dimension ref="A1:AB73"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="12.7265625" bestFit="1" customWidth="1"/>
@@ -1619,1682 +1609,550 @@
     <col min="7" max="7" width="30.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>150</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
       <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A2" s="1">
-        <v>1</v>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>151</v>
       </c>
       <c r="B2">
-        <v>882.00568292830201</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>18142.005682928298</v>
+        <v>1371.51231369231</v>
       </c>
       <c r="D2">
-        <v>0.124358974358974</v>
+        <v>19331.512313692299</v>
       </c>
       <c r="E2">
+        <v>0.15504807692307601</v>
+      </c>
+      <c r="F2">
+        <v>39</v>
+      </c>
+      <c r="G2">
+        <v>8</v>
+      </c>
+      <c r="H2">
+        <v>4.375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>10261.1121248043</v>
+      </c>
+      <c r="D3">
+        <v>27941.112124804298</v>
+      </c>
+      <c r="E3">
+        <v>0.179102564102564</v>
+      </c>
+      <c r="F3">
+        <v>81</v>
+      </c>
+      <c r="G3">
+        <v>11</v>
+      </c>
+      <c r="H3">
+        <v>1.8181818181818099</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>184.917752544639</v>
+      </c>
+      <c r="D4">
+        <v>19264.917752544599</v>
+      </c>
+      <c r="E4">
+        <v>0.14833333333333301</v>
+      </c>
+      <c r="F4">
+        <v>105</v>
+      </c>
+      <c r="G4">
+        <v>8</v>
+      </c>
+      <c r="H4">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>-923.48986154901604</v>
+      </c>
+      <c r="D5">
+        <v>17576.5101384509</v>
+      </c>
+      <c r="E5">
+        <v>0.15625</v>
+      </c>
+      <c r="F5">
+        <v>72</v>
+      </c>
+      <c r="G5">
+        <v>7</v>
+      </c>
+      <c r="H5">
+        <v>0.57142857142857095</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>-4969.9329346362902</v>
+      </c>
+      <c r="D6">
+        <v>13530.067065363701</v>
+      </c>
+      <c r="E6">
+        <v>0.132051282051282</v>
+      </c>
+      <c r="F6">
+        <v>46</v>
+      </c>
+      <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6">
+        <v>10.5714285714285</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>1100.28695877111</v>
+      </c>
+      <c r="D7">
+        <v>20740.286958771099</v>
+      </c>
+      <c r="E7">
+        <v>0.1525</v>
+      </c>
+      <c r="F7">
+        <v>72</v>
+      </c>
+      <c r="G7">
+        <v>9</v>
+      </c>
+      <c r="H7">
+        <v>1.55555555555555</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>-948.02027051110394</v>
+      </c>
+      <c r="D8">
+        <v>18451.979729488801</v>
+      </c>
+      <c r="E8">
+        <v>0.10801282051282</v>
+      </c>
+      <c r="F8">
+        <v>42</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+      <c r="H8">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>-7637.4254553803903</v>
+      </c>
+      <c r="D9">
+        <v>11862.5745446196</v>
+      </c>
+      <c r="E9">
+        <v>0.13878205128205101</v>
+      </c>
+      <c r="F9">
+        <v>48</v>
+      </c>
+      <c r="G9">
+        <v>7</v>
+      </c>
+      <c r="H9">
+        <v>8.71428571428571</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>6402.7920894414401</v>
+      </c>
+      <c r="D10">
+        <v>23662.792089441398</v>
+      </c>
+      <c r="E10">
+        <v>0.146666666666666</v>
+      </c>
+      <c r="F10">
+        <v>48</v>
+      </c>
+      <c r="G10">
+        <v>9</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11">
+        <v>-8732.8115855182405</v>
+      </c>
+      <c r="D11">
+        <v>9547.1884144817504</v>
+      </c>
+      <c r="E11">
+        <v>0.137072649572649</v>
+      </c>
+      <c r="F11">
+        <v>58</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+      <c r="H11">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12">
+        <v>10799.540495993</v>
+      </c>
+      <c r="D12">
+        <v>27579.540495992998</v>
+      </c>
+      <c r="E12">
+        <v>0.22211538461538399</v>
+      </c>
+      <c r="F12">
+        <v>91</v>
+      </c>
+      <c r="G12">
+        <v>13</v>
+      </c>
+      <c r="H12">
+        <v>2.6153846153846101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13">
+        <v>15307.991134014999</v>
+      </c>
+      <c r="D13">
+        <v>32507.991134014999</v>
+      </c>
+      <c r="E13">
+        <v>0.21196581196581099</v>
+      </c>
+      <c r="F13">
+        <v>18</v>
+      </c>
+      <c r="G13">
+        <v>8</v>
+      </c>
+      <c r="H13">
+        <v>2.875</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B14">
+        <v>13</v>
+      </c>
+      <c r="C14">
+        <v>-6053.2461802180396</v>
+      </c>
+      <c r="D14">
+        <v>11046.753819781899</v>
+      </c>
+      <c r="E14">
+        <v>0.15384615384615299</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>4</v>
+      </c>
+      <c r="H14">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B15">
+        <v>14</v>
+      </c>
+      <c r="C15">
+        <v>-38.643658467652102</v>
+      </c>
+      <c r="D15">
+        <v>16961.356341532301</v>
+      </c>
+      <c r="E15">
+        <v>0.218162393162393</v>
+      </c>
+      <c r="F15">
+        <v>68</v>
+      </c>
+      <c r="G15">
+        <v>7</v>
+      </c>
+      <c r="H15">
+        <v>4.71428571428571</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B16">
+        <v>15</v>
+      </c>
+      <c r="C16">
+        <v>6629.6625097844499</v>
+      </c>
+      <c r="D16">
+        <v>24229.662509784401</v>
+      </c>
+      <c r="E16">
+        <v>0.15064102564102499</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>4</v>
+      </c>
+      <c r="H16">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B17">
         <v>16</v>
       </c>
-      <c r="F2">
+      <c r="C17">
+        <v>6686.6475843882899</v>
+      </c>
+      <c r="D17">
+        <v>24406.6475843882</v>
+      </c>
+      <c r="E17">
+        <v>0.14449786324786301</v>
+      </c>
+      <c r="F17">
+        <v>94</v>
+      </c>
+      <c r="G17">
+        <v>9</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B18">
+        <v>17</v>
+      </c>
+      <c r="C18">
+        <v>4287.3477770127802</v>
+      </c>
+      <c r="D18">
+        <v>21767.347777012699</v>
+      </c>
+      <c r="E18">
+        <v>0.20683760683760599</v>
+      </c>
+      <c r="F18">
+        <v>68</v>
+      </c>
+      <c r="G18">
+        <v>7</v>
+      </c>
+      <c r="H18">
+        <v>4.8571428571428497</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B19">
+        <v>18</v>
+      </c>
+      <c r="C19">
+        <v>-2208.3910090171798</v>
+      </c>
+      <c r="D19">
+        <v>15031.608990982801</v>
+      </c>
+      <c r="E19">
+        <v>0.147435897435897</v>
+      </c>
+      <c r="F19">
+        <v>84</v>
+      </c>
+      <c r="G19">
+        <v>8</v>
+      </c>
+      <c r="H19">
+        <v>1.875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B20">
+        <v>19</v>
+      </c>
+      <c r="C20">
+        <v>-5707.4107610163801</v>
+      </c>
+      <c r="D20">
+        <v>12692.589238983601</v>
+      </c>
+      <c r="E20">
+        <v>0.123076923076923</v>
+      </c>
+      <c r="F20">
+        <v>16</v>
+      </c>
+      <c r="G20">
         <v>3</v>
       </c>
-      <c r="G2">
-        <v>2.3333333333333299</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>-7533.09961834561</v>
-      </c>
-      <c r="C3">
-        <v>8666.9003816543809</v>
-      </c>
-      <c r="D3">
-        <v>0.13547008547008499</v>
-      </c>
-      <c r="E3">
-        <v>57</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>-8895.3730901090203</v>
-      </c>
-      <c r="C4">
-        <v>8704.6269098909706</v>
-      </c>
-      <c r="D4">
-        <v>0.144230769230769</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>-11967.2583236965</v>
-      </c>
-      <c r="C5">
-        <v>4432.7416763034498</v>
-      </c>
-      <c r="D5">
-        <v>0.18269230769230699</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>-554.42880021302699</v>
-      </c>
-      <c r="C6">
-        <v>15845.5711997869</v>
-      </c>
-      <c r="D6">
-        <v>0.131410256410256</v>
-      </c>
-      <c r="E6">
-        <v>25</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>0.33333333333333298</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>-8458.6376799110294</v>
-      </c>
-      <c r="C7">
-        <v>7941.3623200889597</v>
-      </c>
-      <c r="D7">
-        <v>0.11752136752136701</v>
-      </c>
-      <c r="E7">
-        <v>35</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-      <c r="G7">
-        <v>5.2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>-8430.6301590337298</v>
-      </c>
-      <c r="C8">
-        <v>7669.3698409662602</v>
-      </c>
-      <c r="D8">
-        <v>0.114743589743589</v>
-      </c>
-      <c r="E8">
-        <v>58</v>
-      </c>
-      <c r="F8">
-        <v>5</v>
-      </c>
-      <c r="G8">
-        <v>3.4</v>
-      </c>
-      <c r="M8" t="s">
-        <v>12</v>
-      </c>
-      <c r="N8" t="s">
-        <v>13</v>
-      </c>
-      <c r="O8" t="s">
-        <v>14</v>
-      </c>
-      <c r="P8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A9" s="1">
+      <c r="H20">
+        <v>3.6666666666666599</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B21">
+        <v>20</v>
+      </c>
+      <c r="C21">
+        <v>2347.2101712049198</v>
+      </c>
+      <c r="D21">
+        <v>21727.210171204901</v>
+      </c>
+      <c r="E21">
+        <v>0.14435897435897399</v>
+      </c>
+      <c r="F21">
+        <v>83</v>
+      </c>
+      <c r="G21">
         <v>8</v>
       </c>
-      <c r="B9">
-        <v>-5846.6230901090203</v>
-      </c>
-      <c r="C9">
-        <v>10853.3769098909</v>
-      </c>
-      <c r="D9">
-        <v>0.15384615384615299</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>2</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="M9" t="s">
-        <v>16</v>
-      </c>
-      <c r="N9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O9">
-        <v>8532.52668654833</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>69.5541267630433</v>
-      </c>
-      <c r="C10">
-        <v>14689.554126763</v>
-      </c>
-      <c r="D10">
-        <v>0.13935897435897401</v>
-      </c>
-      <c r="E10">
-        <v>93</v>
-      </c>
-      <c r="F10">
-        <v>7</v>
-      </c>
-      <c r="G10">
-        <v>5.1428571428571397</v>
-      </c>
-      <c r="M10" t="s">
-        <v>18</v>
-      </c>
-      <c r="N10" t="s">
-        <v>17</v>
-      </c>
-      <c r="O10">
-        <v>25432.526686548299</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>-5984.14692217216</v>
-      </c>
-      <c r="C11">
-        <v>9415.8530778278291</v>
-      </c>
-      <c r="D11">
-        <v>0.12419871794871699</v>
-      </c>
-      <c r="E11">
-        <v>50</v>
-      </c>
-      <c r="F11">
-        <v>6</v>
-      </c>
-      <c r="G11">
-        <v>6.6666666666666599</v>
-      </c>
-      <c r="M11" t="s">
-        <v>19</v>
-      </c>
-      <c r="N11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12">
-        <v>8532.52668654833</v>
-      </c>
-      <c r="C12">
-        <v>25432.526686548299</v>
-      </c>
-      <c r="D12">
-        <v>0.12355769230769199</v>
-      </c>
-      <c r="E12">
-        <v>14</v>
-      </c>
-      <c r="F12">
-        <v>7</v>
-      </c>
-      <c r="G12">
-        <v>0.14285714285714199</v>
-      </c>
-      <c r="M12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13">
-        <v>-2573.1687178673801</v>
-      </c>
-      <c r="C13">
-        <v>13426.8312821326</v>
-      </c>
-      <c r="D13">
-        <v>0.118589743589743</v>
-      </c>
-      <c r="E13">
-        <v>16</v>
-      </c>
-      <c r="F13">
-        <v>5</v>
-      </c>
-      <c r="G13">
-        <v>3.2</v>
-      </c>
-      <c r="M13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13" t="s">
-        <v>22</v>
-      </c>
-      <c r="P13">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A14" s="1">
-        <v>13</v>
-      </c>
-      <c r="B14">
-        <v>-846.87713426424295</v>
-      </c>
-      <c r="C14">
-        <v>15253.122865735701</v>
-      </c>
-      <c r="D14">
-        <v>0.110897435897435</v>
-      </c>
-      <c r="E14">
-        <v>50</v>
-      </c>
-      <c r="F14">
-        <v>5</v>
-      </c>
-      <c r="G14">
-        <v>6.8</v>
-      </c>
-      <c r="M14" t="s">
-        <v>23</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14" t="s">
-        <v>22</v>
-      </c>
-      <c r="P14">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A15" s="1">
-        <v>14</v>
-      </c>
-      <c r="B15">
-        <v>-14803.9757567784</v>
-      </c>
-      <c r="C15">
-        <v>1896.0242432215</v>
-      </c>
-      <c r="D15">
-        <v>0.130128205128205</v>
-      </c>
-      <c r="E15">
-        <v>43</v>
-      </c>
-      <c r="F15">
-        <v>3</v>
-      </c>
-      <c r="G15">
-        <v>11</v>
-      </c>
-      <c r="M15" t="s">
-        <v>24</v>
-      </c>
-      <c r="N15">
-        <v>2</v>
-      </c>
-      <c r="O15" t="s">
-        <v>22</v>
-      </c>
-      <c r="P15">
-        <v>2</v>
-      </c>
-      <c r="Q15">
-        <v>3</v>
-      </c>
-      <c r="R15">
-        <v>2</v>
-      </c>
-      <c r="S15" t="s">
-        <v>22</v>
-      </c>
-      <c r="T15">
-        <v>153</v>
-      </c>
-      <c r="U15">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A16" s="1">
-        <v>15</v>
-      </c>
-      <c r="B16">
-        <v>2425.9958629309399</v>
-      </c>
-      <c r="C16">
-        <v>18625.9958629309</v>
-      </c>
-      <c r="D16">
-        <v>0.13215811965811899</v>
-      </c>
-      <c r="E16">
-        <v>19</v>
-      </c>
-      <c r="F16">
-        <v>5</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-      <c r="M16" t="s">
-        <v>25</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16" t="s">
-        <v>22</v>
-      </c>
-      <c r="P16">
-        <v>2</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A17" s="1">
-        <v>16</v>
-      </c>
-      <c r="B17">
-        <v>-9612.7537923132004</v>
-      </c>
-      <c r="C17">
-        <v>8287.2462076867996</v>
-      </c>
-      <c r="D17">
-        <v>0.124358974358974</v>
-      </c>
-      <c r="E17">
-        <v>14</v>
-      </c>
-      <c r="F17">
-        <v>3</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-      <c r="M17" t="s">
-        <v>26</v>
-      </c>
-      <c r="N17">
-        <v>2</v>
-      </c>
-      <c r="O17" t="s">
-        <v>22</v>
-      </c>
-      <c r="P17">
-        <v>3</v>
-      </c>
-      <c r="Q17">
-        <v>5</v>
-      </c>
-      <c r="R17">
-        <v>3</v>
-      </c>
-      <c r="S17" t="s">
-        <v>22</v>
-      </c>
-      <c r="T17">
-        <v>106</v>
-      </c>
-      <c r="U17">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A18" s="1">
-        <v>17</v>
-      </c>
-      <c r="B18">
-        <v>-9925.8093128338096</v>
-      </c>
-      <c r="C18">
-        <v>8234.1906871661795</v>
-      </c>
-      <c r="D18">
-        <v>0.13701923076923</v>
-      </c>
-      <c r="E18">
-        <v>23</v>
-      </c>
-      <c r="F18">
-        <v>3</v>
-      </c>
-      <c r="G18">
-        <v>0.66666666666666596</v>
-      </c>
-      <c r="M18" t="s">
-        <v>27</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18" t="s">
-        <v>22</v>
-      </c>
-      <c r="P18">
-        <v>3</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A19" s="1">
-        <v>18</v>
-      </c>
-      <c r="B19">
-        <v>-5347.7101446090601</v>
-      </c>
-      <c r="C19">
-        <v>12552.2898553909</v>
-      </c>
-      <c r="D19">
-        <v>0.132051282051282</v>
-      </c>
-      <c r="E19">
-        <v>26</v>
-      </c>
-      <c r="F19">
-        <v>3</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="M19" t="s">
-        <v>28</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19" t="s">
-        <v>22</v>
-      </c>
-      <c r="P19">
-        <v>4</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A20" s="1">
-        <v>19</v>
-      </c>
-      <c r="B20">
-        <v>-11834.359614403</v>
-      </c>
-      <c r="C20">
-        <v>6365.6403855969402</v>
-      </c>
-      <c r="D20">
-        <v>0.119551282051282</v>
-      </c>
-      <c r="E20">
-        <v>48</v>
-      </c>
-      <c r="F20">
-        <v>6</v>
-      </c>
-      <c r="G20">
-        <v>8.1666666666666607</v>
-      </c>
-      <c r="M20" t="s">
-        <v>29</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20" t="s">
-        <v>22</v>
-      </c>
-      <c r="P20">
-        <v>4</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A21" s="1">
-        <v>20</v>
-      </c>
-      <c r="B21">
-        <v>-3190.9083698080699</v>
-      </c>
-      <c r="C21">
-        <v>14069.091630191901</v>
-      </c>
-      <c r="D21">
-        <v>0.149786324786324</v>
-      </c>
-      <c r="E21">
-        <v>35</v>
-      </c>
-      <c r="F21">
-        <v>6</v>
-      </c>
-      <c r="G21">
-        <v>4.8333333333333304</v>
-      </c>
-      <c r="M21" t="s">
-        <v>30</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21" t="s">
-        <v>22</v>
-      </c>
-      <c r="P21">
-        <v>5</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="M22" t="s">
-        <v>31</v>
-      </c>
-      <c r="N22">
-        <v>2</v>
-      </c>
-      <c r="O22" t="s">
-        <v>22</v>
-      </c>
-      <c r="P22">
-        <v>5</v>
-      </c>
-      <c r="Q22">
-        <v>6</v>
-      </c>
-      <c r="R22">
-        <v>5</v>
-      </c>
-      <c r="S22" t="s">
-        <v>22</v>
-      </c>
-      <c r="T22">
-        <v>216</v>
-      </c>
-      <c r="U22">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>84</v>
-      </c>
-      <c r="B23">
-        <f>AVERAGE(B2:B21)</f>
-        <v>-5194.7839083648332</v>
-      </c>
-      <c r="C23">
-        <f t="shared" ref="C23:G23" si="0">AVERAGE(C2:C21)</f>
-        <v>11525.216091635133</v>
-      </c>
-      <c r="D23">
-        <f t="shared" si="0"/>
-        <v>0.13229647435897382</v>
-      </c>
-      <c r="E23">
-        <f t="shared" si="0"/>
-        <v>31.6</v>
-      </c>
-      <c r="F23">
-        <f t="shared" si="0"/>
-        <v>4.3</v>
-      </c>
-      <c r="G23">
-        <f t="shared" si="0"/>
-        <v>3.6142857142857125</v>
-      </c>
-      <c r="M23" t="s">
-        <v>32</v>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23" t="s">
-        <v>22</v>
-      </c>
-      <c r="P23">
-        <v>6</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>85</v>
-      </c>
-      <c r="B24">
-        <f>_xlfn.STDEV.S(B2:B21)</f>
-        <v>5749.2628346274678</v>
-      </c>
-      <c r="C24">
-        <f t="shared" ref="C24:G24" si="1">_xlfn.STDEV.S(C2:C21)</f>
-        <v>5529.9826775233105</v>
-      </c>
-      <c r="D24">
-        <f t="shared" si="1"/>
-        <v>1.6452260616045433E-2</v>
-      </c>
-      <c r="E24">
-        <f t="shared" si="1"/>
-        <v>23.043208840875668</v>
-      </c>
-      <c r="F24">
-        <f t="shared" si="1"/>
-        <v>1.6575187543592473</v>
-      </c>
-      <c r="G24">
-        <f t="shared" si="1"/>
-        <v>3.1283774444616035</v>
-      </c>
-      <c r="M24" t="s">
-        <v>33</v>
-      </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24" t="s">
-        <v>22</v>
-      </c>
-      <c r="P24">
-        <v>6</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="M25" t="s">
-        <v>34</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25" t="s">
-        <v>22</v>
-      </c>
-      <c r="P25">
-        <v>7</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="M26" t="s">
-        <v>35</v>
-      </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26" t="s">
-        <v>22</v>
-      </c>
-      <c r="P26">
-        <v>7</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="M27" t="s">
-        <v>36</v>
-      </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27" t="s">
-        <v>22</v>
-      </c>
-      <c r="P27">
-        <v>8</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="M28" t="s">
-        <v>37</v>
-      </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28" t="s">
-        <v>22</v>
-      </c>
-      <c r="P28">
-        <v>8</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="M29" t="s">
-        <v>38</v>
-      </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
-      <c r="O29" t="s">
-        <v>22</v>
-      </c>
-      <c r="P29">
-        <v>9</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="M30" t="s">
-        <v>39</v>
-      </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
-      <c r="O30" t="s">
-        <v>22</v>
-      </c>
-      <c r="P30">
-        <v>9</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="M31" t="s">
-        <v>40</v>
-      </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
-      <c r="O31" t="s">
-        <v>22</v>
-      </c>
-      <c r="P31">
-        <v>10</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="M32" t="s">
-        <v>41</v>
-      </c>
-      <c r="N32">
-        <v>2</v>
-      </c>
-      <c r="O32" t="s">
-        <v>22</v>
-      </c>
-      <c r="P32">
-        <v>10</v>
-      </c>
-      <c r="Q32">
-        <v>4</v>
-      </c>
-      <c r="R32">
-        <v>1</v>
-      </c>
-      <c r="S32" t="s">
-        <v>22</v>
-      </c>
-      <c r="T32">
-        <v>92</v>
-      </c>
-      <c r="U32">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="33" spans="13:28" x14ac:dyDescent="0.35">
-      <c r="M33" t="s">
-        <v>42</v>
-      </c>
-      <c r="N33" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="34" spans="13:28" x14ac:dyDescent="0.35">
-      <c r="M34" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35" spans="13:28" x14ac:dyDescent="0.35">
-      <c r="M35" t="s">
-        <v>44</v>
-      </c>
-      <c r="N35">
-        <v>2</v>
-      </c>
-      <c r="O35" t="s">
-        <v>22</v>
-      </c>
-      <c r="P35" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q35">
-        <v>20</v>
-      </c>
-      <c r="R35" t="s">
-        <v>22</v>
-      </c>
-      <c r="S35" t="s">
-        <v>46</v>
-      </c>
-      <c r="T35" t="s">
-        <v>47</v>
-      </c>
-      <c r="U35" t="s">
-        <v>22</v>
-      </c>
-      <c r="V35">
-        <v>10</v>
-      </c>
-      <c r="W35" t="s">
-        <v>48</v>
-      </c>
-      <c r="X35">
-        <v>4</v>
-      </c>
-      <c r="Y35" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z35" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA35" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB35" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="36" spans="13:28" x14ac:dyDescent="0.35">
-      <c r="M36" t="s">
-        <v>44</v>
-      </c>
-      <c r="N36">
-        <v>60</v>
-      </c>
-      <c r="O36" t="s">
-        <v>22</v>
-      </c>
-      <c r="P36" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q36">
-        <v>20</v>
-      </c>
-      <c r="R36" t="s">
-        <v>22</v>
-      </c>
-      <c r="S36" t="s">
-        <v>46</v>
-      </c>
-      <c r="T36" t="s">
-        <v>50</v>
-      </c>
-      <c r="U36" t="s">
-        <v>22</v>
-      </c>
-      <c r="V36">
-        <v>4</v>
-      </c>
-      <c r="W36" t="s">
-        <v>48</v>
-      </c>
-      <c r="X36">
-        <v>1</v>
-      </c>
-      <c r="Y36" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z36" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA36" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB36" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="37" spans="13:28" x14ac:dyDescent="0.35">
-      <c r="M37" t="s">
-        <v>44</v>
-      </c>
-      <c r="N37">
-        <v>21</v>
-      </c>
-      <c r="O37" t="s">
-        <v>22</v>
-      </c>
-      <c r="P37" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q37">
-        <v>3</v>
-      </c>
-      <c r="R37" t="s">
-        <v>22</v>
-      </c>
-      <c r="S37" t="s">
-        <v>46</v>
-      </c>
-      <c r="T37" t="s">
-        <v>47</v>
-      </c>
-      <c r="U37" t="s">
-        <v>22</v>
-      </c>
-      <c r="V37">
-        <v>2</v>
-      </c>
-      <c r="W37" t="s">
-        <v>48</v>
-      </c>
-      <c r="X37">
-        <v>3</v>
-      </c>
-      <c r="Y37" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z37" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA37" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB37" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="38" spans="13:28" x14ac:dyDescent="0.35">
-      <c r="M38" t="s">
-        <v>44</v>
-      </c>
-      <c r="N38">
-        <v>52</v>
-      </c>
-      <c r="O38" t="s">
-        <v>22</v>
-      </c>
-      <c r="P38" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q38">
-        <v>3</v>
-      </c>
-      <c r="R38" t="s">
-        <v>22</v>
-      </c>
-      <c r="S38" t="s">
-        <v>46</v>
-      </c>
-      <c r="T38" t="s">
-        <v>50</v>
-      </c>
-      <c r="U38" t="s">
-        <v>22</v>
-      </c>
-      <c r="V38">
-        <v>3</v>
-      </c>
-      <c r="W38" t="s">
-        <v>48</v>
-      </c>
-      <c r="X38">
-        <v>2</v>
-      </c>
-      <c r="Y38" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z38" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA38" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB38" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="39" spans="13:28" x14ac:dyDescent="0.35">
-      <c r="M39" t="s">
-        <v>44</v>
-      </c>
-      <c r="N39">
-        <v>18</v>
-      </c>
-      <c r="O39" t="s">
-        <v>22</v>
-      </c>
-      <c r="P39" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q39">
-        <v>5</v>
-      </c>
-      <c r="R39" t="s">
-        <v>22</v>
-      </c>
-      <c r="S39" t="s">
-        <v>46</v>
-      </c>
-      <c r="T39" t="s">
-        <v>50</v>
-      </c>
-      <c r="U39" t="s">
-        <v>22</v>
-      </c>
-      <c r="V39">
-        <v>5</v>
-      </c>
-      <c r="W39" t="s">
-        <v>48</v>
-      </c>
-      <c r="X39">
-        <v>3</v>
-      </c>
-      <c r="Y39" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z39" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA39" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB39" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="40" spans="13:28" x14ac:dyDescent="0.35">
-      <c r="M40" t="s">
-        <v>44</v>
-      </c>
-      <c r="N40">
-        <v>27</v>
-      </c>
-      <c r="O40" t="s">
-        <v>22</v>
-      </c>
-      <c r="P40" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q40">
-        <v>10</v>
-      </c>
-      <c r="R40" t="s">
-        <v>22</v>
-      </c>
-      <c r="S40" t="s">
-        <v>46</v>
-      </c>
-      <c r="T40" t="s">
-        <v>47</v>
-      </c>
-      <c r="U40" t="s">
-        <v>22</v>
-      </c>
-      <c r="V40">
-        <v>5</v>
-      </c>
-      <c r="W40" t="s">
-        <v>48</v>
-      </c>
-      <c r="X40">
-        <v>6</v>
-      </c>
-      <c r="Y40" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z40" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA40" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB40" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="41" spans="13:28" x14ac:dyDescent="0.35">
-      <c r="M41" t="s">
-        <v>44</v>
-      </c>
-      <c r="N41">
-        <v>7</v>
-      </c>
-      <c r="O41" t="s">
-        <v>22</v>
-      </c>
-      <c r="P41" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q41">
-        <v>5</v>
-      </c>
-      <c r="R41" t="s">
-        <v>22</v>
-      </c>
-      <c r="S41" t="s">
-        <v>46</v>
-      </c>
-      <c r="T41" t="s">
-        <v>47</v>
-      </c>
-      <c r="U41" t="s">
-        <v>22</v>
-      </c>
-      <c r="V41">
-        <v>3</v>
-      </c>
-      <c r="W41" t="s">
-        <v>48</v>
-      </c>
-      <c r="X41">
-        <v>5</v>
-      </c>
-      <c r="Y41" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z41" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA41" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB41" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="42" spans="13:28" x14ac:dyDescent="0.35">
-      <c r="M42" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="43" spans="13:28" x14ac:dyDescent="0.35">
-      <c r="M43" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45" spans="13:28" x14ac:dyDescent="0.35">
-      <c r="M45" t="s">
-        <v>54</v>
-      </c>
-      <c r="N45">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="13:28" x14ac:dyDescent="0.35">
-      <c r="M46" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="47" spans="13:28" x14ac:dyDescent="0.35">
-      <c r="M47" t="s">
-        <v>55</v>
-      </c>
-      <c r="N47" t="s">
-        <v>56</v>
-      </c>
-      <c r="O47" t="s">
-        <v>57</v>
-      </c>
-      <c r="P47" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>59</v>
-      </c>
-      <c r="R47" t="s">
-        <v>60</v>
-      </c>
-      <c r="S47" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="48" spans="13:28" x14ac:dyDescent="0.35">
-      <c r="M48" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="49" spans="13:19" x14ac:dyDescent="0.35">
-      <c r="M49">
-        <v>1</v>
-      </c>
-      <c r="N49">
-        <v>2</v>
-      </c>
-      <c r="O49">
-        <v>3</v>
-      </c>
-      <c r="P49">
-        <v>153</v>
-      </c>
-      <c r="Q49">
-        <v>180</v>
-      </c>
-      <c r="R49">
-        <v>27</v>
-      </c>
-      <c r="S49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="13:19" x14ac:dyDescent="0.35">
-      <c r="M50">
-        <v>2</v>
-      </c>
-      <c r="N50">
-        <v>3</v>
-      </c>
-      <c r="O50">
-        <v>2</v>
-      </c>
-      <c r="P50">
-        <v>611</v>
-      </c>
-      <c r="Q50">
-        <v>638</v>
-      </c>
-      <c r="R50">
-        <v>27</v>
-      </c>
-      <c r="S50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="13:19" x14ac:dyDescent="0.35">
-      <c r="M52" t="s">
-        <v>54</v>
-      </c>
-      <c r="N52">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="13:19" x14ac:dyDescent="0.35">
-      <c r="M53" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="54" spans="13:19" x14ac:dyDescent="0.35">
-      <c r="M54" t="s">
-        <v>55</v>
-      </c>
-      <c r="N54" t="s">
-        <v>56</v>
-      </c>
-      <c r="O54" t="s">
-        <v>57</v>
-      </c>
-      <c r="P54" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q54" t="s">
-        <v>59</v>
-      </c>
-      <c r="R54" t="s">
-        <v>60</v>
-      </c>
-      <c r="S54" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="55" spans="13:19" x14ac:dyDescent="0.35">
-      <c r="M55" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="56" spans="13:19" x14ac:dyDescent="0.35">
-      <c r="M56">
-        <v>1</v>
-      </c>
-      <c r="N56">
-        <v>3</v>
-      </c>
-      <c r="O56">
-        <v>5</v>
-      </c>
-      <c r="P56">
-        <v>106</v>
-      </c>
-      <c r="Q56">
-        <v>119</v>
-      </c>
-      <c r="R56">
-        <v>13</v>
-      </c>
-      <c r="S56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="13:19" x14ac:dyDescent="0.35">
-      <c r="M57">
-        <v>2</v>
-      </c>
-      <c r="N57">
-        <v>5</v>
-      </c>
-      <c r="O57">
-        <v>3</v>
-      </c>
-      <c r="P57">
-        <v>149</v>
-      </c>
-      <c r="Q57">
-        <v>162</v>
-      </c>
-      <c r="R57">
-        <v>13</v>
-      </c>
-      <c r="S57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="13:19" x14ac:dyDescent="0.35">
-      <c r="M59" t="s">
-        <v>54</v>
-      </c>
-      <c r="N59">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="60" spans="13:19" x14ac:dyDescent="0.35">
-      <c r="M60" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="61" spans="13:19" x14ac:dyDescent="0.35">
-      <c r="M61" t="s">
-        <v>55</v>
-      </c>
-      <c r="N61" t="s">
-        <v>56</v>
-      </c>
-      <c r="O61" t="s">
-        <v>57</v>
-      </c>
-      <c r="P61" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q61" t="s">
-        <v>59</v>
-      </c>
-      <c r="R61" t="s">
-        <v>60</v>
-      </c>
-      <c r="S61" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="62" spans="13:19" x14ac:dyDescent="0.35">
-      <c r="M62" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="13:19" x14ac:dyDescent="0.35">
-      <c r="M63">
-        <v>1</v>
-      </c>
-      <c r="N63">
-        <v>5</v>
-      </c>
-      <c r="O63">
-        <v>6</v>
-      </c>
-      <c r="P63">
-        <v>216</v>
-      </c>
-      <c r="Q63">
-        <v>230</v>
-      </c>
-      <c r="R63">
-        <v>14</v>
-      </c>
-      <c r="S63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="13:19" x14ac:dyDescent="0.35">
-      <c r="M64">
-        <v>2</v>
-      </c>
-      <c r="N64">
-        <v>6</v>
-      </c>
-      <c r="O64">
-        <v>5</v>
-      </c>
-      <c r="P64">
-        <v>260</v>
-      </c>
-      <c r="Q64">
-        <v>274</v>
-      </c>
-      <c r="R64">
-        <v>14</v>
-      </c>
-      <c r="S64">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="66" spans="13:19" x14ac:dyDescent="0.35">
-      <c r="M66" t="s">
-        <v>54</v>
-      </c>
-      <c r="N66">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="67" spans="13:19" x14ac:dyDescent="0.35">
-      <c r="M67" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="68" spans="13:19" x14ac:dyDescent="0.35">
-      <c r="M68" t="s">
-        <v>55</v>
-      </c>
-      <c r="N68" t="s">
-        <v>56</v>
-      </c>
-      <c r="O68" t="s">
-        <v>57</v>
-      </c>
-      <c r="P68" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q68" t="s">
-        <v>59</v>
-      </c>
-      <c r="R68" t="s">
-        <v>60</v>
-      </c>
-      <c r="S68" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="69" spans="13:19" x14ac:dyDescent="0.35">
-      <c r="M69" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="70" spans="13:19" x14ac:dyDescent="0.35">
-      <c r="M70">
-        <v>1</v>
-      </c>
-      <c r="N70">
-        <v>10</v>
-      </c>
-      <c r="O70">
-        <v>4</v>
-      </c>
-      <c r="P70">
-        <v>92</v>
-      </c>
-      <c r="Q70">
-        <v>117</v>
-      </c>
-      <c r="R70">
-        <v>25</v>
-      </c>
-      <c r="S70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="13:19" x14ac:dyDescent="0.35">
-      <c r="M71">
-        <v>2</v>
-      </c>
-      <c r="N71">
-        <v>4</v>
-      </c>
-      <c r="O71">
-        <v>1</v>
-      </c>
-      <c r="P71">
-        <v>722</v>
-      </c>
-      <c r="Q71">
-        <v>752</v>
-      </c>
-      <c r="R71">
-        <v>30</v>
-      </c>
-      <c r="S71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="13:19" x14ac:dyDescent="0.35">
-      <c r="M73" t="s">
-        <v>62</v>
-      </c>
-      <c r="N73" t="s">
-        <v>63</v>
-      </c>
-      <c r="O73">
-        <v>8</v>
+      <c r="H21">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4176,7 +3034,7 @@
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B23">
         <f>AVERAGE(B2:B21)</f>
@@ -4220,7 +3078,7 @@
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B24">
         <f>_xlfn.STDEV.S(B2:B21)</f>
@@ -4424,7 +3282,7 @@
         <v>22</v>
       </c>
       <c r="AA33" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="34" spans="12:28" x14ac:dyDescent="0.35">
@@ -4474,7 +3332,7 @@
         <v>22</v>
       </c>
       <c r="AA34" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="35" spans="12:28" x14ac:dyDescent="0.35">
@@ -4524,7 +3382,7 @@
         <v>22</v>
       </c>
       <c r="AA35" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
     </row>
     <row r="36" spans="12:28" x14ac:dyDescent="0.35">
@@ -4550,10 +3408,10 @@
         <v>46</v>
       </c>
       <c r="S36" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="T36" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="U36" t="s">
         <v>22</v>
@@ -4577,7 +3435,7 @@
         <v>22</v>
       </c>
       <c r="AB36" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
     </row>
     <row r="37" spans="12:28" x14ac:dyDescent="0.35">
@@ -4603,7 +3461,7 @@
         <v>46</v>
       </c>
       <c r="S37" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="T37" t="s">
         <v>22</v>
@@ -4627,7 +3485,7 @@
         <v>22</v>
       </c>
       <c r="AA37" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="38" spans="12:28" x14ac:dyDescent="0.35">
@@ -4677,7 +3535,7 @@
         <v>22</v>
       </c>
       <c r="AA38" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="39" spans="12:28" x14ac:dyDescent="0.35">
@@ -4703,7 +3561,7 @@
         <v>46</v>
       </c>
       <c r="S39" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="T39" t="s">
         <v>22</v>
@@ -4727,7 +3585,7 @@
         <v>22</v>
       </c>
       <c r="AA39" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
     </row>
     <row r="40" spans="12:28" x14ac:dyDescent="0.35">
@@ -4777,7 +3635,7 @@
         <v>22</v>
       </c>
       <c r="AA40" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="41" spans="12:28" x14ac:dyDescent="0.35">
@@ -4827,7 +3685,7 @@
         <v>22</v>
       </c>
       <c r="AA41" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="42" spans="12:28" x14ac:dyDescent="0.35">
@@ -4853,10 +3711,10 @@
         <v>46</v>
       </c>
       <c r="S42" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="T42" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="U42" t="s">
         <v>22</v>
@@ -4880,7 +3738,7 @@
         <v>22</v>
       </c>
       <c r="AB42" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="43" spans="12:28" x14ac:dyDescent="0.35">
@@ -6695,7 +5553,7 @@
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B23">
         <f>AVERAGE(B2:B21)</f>
@@ -6739,7 +5597,7 @@
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B24">
         <f>_xlfn.STDEV.S(B2:B21)</f>
@@ -7025,7 +5883,7 @@
         <v>22</v>
       </c>
       <c r="AB32" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" spans="13:28" x14ac:dyDescent="0.35">
@@ -7075,7 +5933,7 @@
         <v>22</v>
       </c>
       <c r="AB33" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="34" spans="13:28" x14ac:dyDescent="0.35">
@@ -7125,7 +5983,7 @@
         <v>22</v>
       </c>
       <c r="AB34" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="13:28" x14ac:dyDescent="0.35">
@@ -7175,7 +6033,7 @@
         <v>22</v>
       </c>
       <c r="AB35" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36" spans="13:28" x14ac:dyDescent="0.35">
@@ -7225,7 +6083,7 @@
         <v>22</v>
       </c>
       <c r="AB36" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="37" spans="13:28" x14ac:dyDescent="0.35">
@@ -7251,7 +6109,7 @@
         <v>46</v>
       </c>
       <c r="T37" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="U37" t="s">
         <v>22</v>
@@ -7275,7 +6133,7 @@
         <v>22</v>
       </c>
       <c r="AB37" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="38" spans="13:28" x14ac:dyDescent="0.35">
@@ -7325,7 +6183,7 @@
         <v>22</v>
       </c>
       <c r="AB38" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="39" spans="13:28" x14ac:dyDescent="0.35">
@@ -7375,7 +6233,7 @@
         <v>22</v>
       </c>
       <c r="AB39" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="40" spans="13:28" x14ac:dyDescent="0.35">
@@ -7425,7 +6283,7 @@
         <v>22</v>
       </c>
       <c r="AB40" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="41" spans="13:28" x14ac:dyDescent="0.35">
@@ -7475,7 +6333,7 @@
         <v>22</v>
       </c>
       <c r="AB41" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="42" spans="13:28" x14ac:dyDescent="0.35">
@@ -7525,7 +6383,7 @@
         <v>22</v>
       </c>
       <c r="AB42" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="43" spans="13:28" x14ac:dyDescent="0.35">
@@ -7551,7 +6409,7 @@
         <v>46</v>
       </c>
       <c r="T43" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="U43" t="s">
         <v>22</v>
@@ -7575,7 +6433,7 @@
         <v>22</v>
       </c>
       <c r="AB43" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
     </row>
     <row r="44" spans="13:28" x14ac:dyDescent="0.35">
@@ -7619,13 +6477,13 @@
         <v>22</v>
       </c>
       <c r="Z44" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA44" t="s">
         <v>22</v>
       </c>
       <c r="AB44" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="45" spans="13:28" x14ac:dyDescent="0.35">
@@ -8658,7 +7516,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -9399,7 +8257,7 @@
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B23">
         <f>AVERAGE(B2:B21)</f>
@@ -9443,7 +8301,7 @@
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B24">
         <f>_xlfn.STDEV.S(B2:B21)</f>
@@ -9677,7 +8535,7 @@
         <v>22</v>
       </c>
       <c r="AA33" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" spans="12:27" x14ac:dyDescent="0.35">
@@ -9703,7 +8561,7 @@
         <v>46</v>
       </c>
       <c r="S34" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="T34" t="s">
         <v>22</v>
@@ -9727,7 +8585,7 @@
         <v>22</v>
       </c>
       <c r="AA34" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="12:27" x14ac:dyDescent="0.35">
@@ -9753,7 +8611,7 @@
         <v>46</v>
       </c>
       <c r="S35" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="T35" t="s">
         <v>22</v>
@@ -9777,7 +8635,7 @@
         <v>22</v>
       </c>
       <c r="AA35" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36" spans="12:27" x14ac:dyDescent="0.35">
@@ -9803,7 +8661,7 @@
         <v>46</v>
       </c>
       <c r="S36" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="T36" t="s">
         <v>22</v>
@@ -9827,7 +8685,7 @@
         <v>22</v>
       </c>
       <c r="AA36" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37" spans="12:27" x14ac:dyDescent="0.35">
@@ -9877,7 +8735,7 @@
         <v>22</v>
       </c>
       <c r="AA37" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="38" spans="12:27" x14ac:dyDescent="0.35">
@@ -9927,7 +8785,7 @@
         <v>22</v>
       </c>
       <c r="AA38" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39" spans="12:27" x14ac:dyDescent="0.35">
@@ -9977,7 +8835,7 @@
         <v>22</v>
       </c>
       <c r="AA39" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="40" spans="12:27" x14ac:dyDescent="0.35">
@@ -10027,7 +8885,7 @@
         <v>22</v>
       </c>
       <c r="AA40" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="41" spans="12:27" x14ac:dyDescent="0.35">
@@ -11225,7 +10083,7 @@
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B23">
         <f>AVERAGE(B2:B21)</f>
@@ -11281,7 +10139,7 @@
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B24">
         <f>_xlfn.STDEV.S(B2:B21)</f>
@@ -11463,7 +10321,7 @@
         <v>22</v>
       </c>
       <c r="AB31" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.35">
@@ -11513,7 +10371,7 @@
         <v>22</v>
       </c>
       <c r="AB32" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="13:28" x14ac:dyDescent="0.35">
@@ -11563,7 +10421,7 @@
         <v>22</v>
       </c>
       <c r="AB33" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="13:28" x14ac:dyDescent="0.35">
@@ -11613,7 +10471,7 @@
         <v>22</v>
       </c>
       <c r="AB34" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="13:28" x14ac:dyDescent="0.35">
@@ -11663,7 +10521,7 @@
         <v>22</v>
       </c>
       <c r="AB35" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="36" spans="13:28" x14ac:dyDescent="0.35">
@@ -11713,7 +10571,7 @@
         <v>22</v>
       </c>
       <c r="AB36" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="13:28" x14ac:dyDescent="0.35">
@@ -11763,7 +10621,7 @@
         <v>22</v>
       </c>
       <c r="AB37" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38" spans="13:28" x14ac:dyDescent="0.35">
@@ -11813,7 +10671,7 @@
         <v>22</v>
       </c>
       <c r="AB38" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39" spans="13:28" x14ac:dyDescent="0.35">
@@ -13105,7 +11963,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B23">
         <f>AVERAGE(B2:B21)</f>
@@ -13149,7 +12007,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B24">
         <f>_xlfn.STDEV.S(B2:B21)</f>
@@ -13376,7 +12234,7 @@
         <v>22</v>
       </c>
       <c r="AB34" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="13:28" x14ac:dyDescent="0.35">
@@ -13426,7 +12284,7 @@
         <v>22</v>
       </c>
       <c r="AB35" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="13:28" x14ac:dyDescent="0.35">
@@ -13476,7 +12334,7 @@
         <v>22</v>
       </c>
       <c r="AB36" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="13:28" x14ac:dyDescent="0.35">
@@ -13526,7 +12384,7 @@
         <v>22</v>
       </c>
       <c r="AB37" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38" spans="13:28" x14ac:dyDescent="0.35">
@@ -13576,7 +12434,7 @@
         <v>22</v>
       </c>
       <c r="AB38" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" spans="13:28" x14ac:dyDescent="0.35">
@@ -13626,7 +12484,7 @@
         <v>22</v>
       </c>
       <c r="AB39" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="40" spans="13:28" x14ac:dyDescent="0.35">
@@ -14793,7 +13651,7 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B23">
         <f>AVERAGE(B2:B21)</f>
@@ -14837,7 +13695,7 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B24">
         <f>_xlfn.STDEV.S(B2:B21)</f>
@@ -15075,7 +13933,7 @@
         <v>22</v>
       </c>
       <c r="AA35" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="36" spans="12:27" x14ac:dyDescent="0.35">
@@ -15125,7 +13983,7 @@
         <v>22</v>
       </c>
       <c r="AA36" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" spans="12:27" x14ac:dyDescent="0.35">
@@ -15175,7 +14033,7 @@
         <v>22</v>
       </c>
       <c r="AA37" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" spans="12:27" x14ac:dyDescent="0.35">
@@ -15225,7 +14083,7 @@
         <v>22</v>
       </c>
       <c r="AA38" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
     </row>
     <row r="39" spans="12:27" x14ac:dyDescent="0.35">
@@ -16103,7 +14961,7 @@
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B23">
         <f>AVERAGE(B2:B21)</f>
@@ -16159,7 +15017,7 @@
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B24">
         <f>_xlfn.STDEV.S(B2:B21)</f>
@@ -16473,7 +15331,7 @@
         <v>22</v>
       </c>
       <c r="AA37" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="12:27" x14ac:dyDescent="0.35">
@@ -16499,7 +15357,7 @@
         <v>46</v>
       </c>
       <c r="S38" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="T38" t="s">
         <v>22</v>
@@ -16523,7 +15381,7 @@
         <v>22</v>
       </c>
       <c r="AA38" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
     </row>
     <row r="39" spans="12:27" x14ac:dyDescent="0.35">
@@ -16573,7 +15431,7 @@
         <v>22</v>
       </c>
       <c r="AA39" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="40" spans="12:27" x14ac:dyDescent="0.35">
@@ -16673,7 +15531,7 @@
         <v>22</v>
       </c>
       <c r="AA41" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="42" spans="12:27" x14ac:dyDescent="0.35">
@@ -16723,7 +15581,7 @@
         <v>22</v>
       </c>
       <c r="AA42" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="43" spans="12:27" x14ac:dyDescent="0.35">
@@ -16773,7 +15631,7 @@
         <v>22</v>
       </c>
       <c r="AA43" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="44" spans="12:27" x14ac:dyDescent="0.35">
@@ -16823,7 +15681,7 @@
         <v>22</v>
       </c>
       <c r="AA44" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="45" spans="12:27" x14ac:dyDescent="0.35">
@@ -16873,7 +15731,7 @@
         <v>22</v>
       </c>
       <c r="AA45" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="46" spans="12:27" x14ac:dyDescent="0.35">
@@ -17481,22 +16339,22 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>-7343.2601668092002</v>
+        <v>19358.938196302199</v>
       </c>
       <c r="C2">
-        <v>9016.7398331907898</v>
+        <v>38518.938196302202</v>
       </c>
       <c r="D2">
-        <v>0.110897435897435</v>
+        <v>0.19578754578754501</v>
       </c>
       <c r="E2">
-        <v>53</v>
+        <v>200</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>3.4166666666666599</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.35">
@@ -17504,22 +16362,22 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2353.0013924333898</v>
+        <v>30924.186194734</v>
       </c>
       <c r="C3">
-        <v>19453.0013924333</v>
+        <v>48924.186194734</v>
       </c>
       <c r="D3">
-        <v>0.127564102564102</v>
+        <v>0.17061965811965801</v>
       </c>
       <c r="E3">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>2.2000000000000002</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.35">
@@ -17527,22 +16385,22 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2761.0546106752299</v>
+        <v>13818.790014979901</v>
       </c>
       <c r="C4">
-        <v>19461.054610675201</v>
+        <v>31318.790014979899</v>
       </c>
       <c r="D4">
-        <v>0.151175213675213</v>
+        <v>0.16707875457875401</v>
       </c>
       <c r="E4">
-        <v>32</v>
+        <v>165</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>6.3333333333333304</v>
+        <v>2.5454545454545401</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.35">
@@ -17550,22 +16408,22 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>-3286.9252560130799</v>
+        <v>33706.481374485702</v>
       </c>
       <c r="C5">
-        <v>13613.074743986899</v>
+        <v>52126.481374485702</v>
       </c>
       <c r="D5">
-        <v>0.203525641025641</v>
+        <v>0.14975961538461499</v>
       </c>
       <c r="E5">
-        <v>62</v>
+        <v>174</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>8.1999999999999993</v>
+        <v>1.6666666666666601</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.35">
@@ -17573,22 +16431,22 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>-6914.2541618482701</v>
+        <v>29263.304218256599</v>
       </c>
       <c r="C6">
-        <v>11285.745838151701</v>
+        <v>47703.304218256599</v>
       </c>
       <c r="D6">
-        <v>0.19230769230769201</v>
+        <v>0.142788461538461</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>9.5</v>
+        <v>1.5454545454545401</v>
       </c>
       <c r="M6" t="s">
         <v>12</v>
@@ -17608,22 +16466,22 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>8679.6241456027692</v>
+        <v>12450.1000582254</v>
       </c>
       <c r="C7">
-        <v>25299.624145602698</v>
+        <v>30570.100058225398</v>
       </c>
       <c r="D7">
-        <v>0.14401709401709401</v>
+        <v>0.19086538461538399</v>
       </c>
       <c r="E7">
-        <v>201</v>
+        <v>113</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G7">
-        <v>2.125</v>
+        <v>8.4285714285714199</v>
       </c>
       <c r="M7" t="s">
         <v>16</v>
@@ -17640,22 +16498,22 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>-1730.94611603202</v>
+        <v>24395.602872040101</v>
       </c>
       <c r="C8">
-        <v>15169.053883967899</v>
+        <v>41815.602872040101</v>
       </c>
       <c r="D8">
-        <v>0.13675213675213599</v>
+        <v>0.18818108974358899</v>
       </c>
       <c r="E8">
-        <v>75</v>
+        <v>186</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G8">
-        <v>11</v>
+        <v>5.0833333333333304</v>
       </c>
       <c r="M8" t="s">
         <v>18</v>
@@ -17672,22 +16530,22 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>-3749.2541618482701</v>
+        <v>27042.410790982602</v>
       </c>
       <c r="C9">
-        <v>14150.745838151701</v>
+        <v>45542.410790982598</v>
       </c>
       <c r="D9">
-        <v>0.19230769230769201</v>
+        <v>0.162692307692307</v>
       </c>
       <c r="E9">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>2.55555555555555</v>
       </c>
       <c r="M9" t="s">
         <v>19</v>
@@ -17701,22 +16559,22 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>-4886.2141587636597</v>
+        <v>18358.0432230437</v>
       </c>
       <c r="C10">
-        <v>11713.7858412363</v>
+        <v>37178.0432230437</v>
       </c>
       <c r="D10">
-        <v>0.124786324786324</v>
+        <v>0.16068376068376</v>
       </c>
       <c r="E10">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G10">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M10" t="s">
         <v>7</v>
@@ -17727,22 +16585,22 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>-5545.2878357258696</v>
+        <v>29072.3305457897</v>
       </c>
       <c r="C11">
-        <v>11154.7121642741</v>
+        <v>49512.3305457897</v>
       </c>
       <c r="D11">
-        <v>0.114903846153846</v>
+        <v>0.175480769230769</v>
       </c>
       <c r="E11">
-        <v>19</v>
+        <v>214</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G11">
-        <v>3.3333333333333299</v>
+        <v>8.3333333333333301E-2</v>
       </c>
       <c r="M11" t="s">
         <v>21</v>
@@ -17783,22 +16641,22 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>-5071.9821695686996</v>
+        <v>32923.529392240802</v>
       </c>
       <c r="C12">
-        <v>11768.017830431199</v>
+        <v>51783.529392240802</v>
       </c>
       <c r="D12">
-        <v>0.152003205128205</v>
+        <v>0.14672364672364599</v>
       </c>
       <c r="E12">
-        <v>107</v>
+        <v>163</v>
       </c>
       <c r="F12">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>5.0833333333333304</v>
       </c>
       <c r="M12" t="s">
         <v>23</v>
@@ -17833,22 +16691,22 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>-10821.7161526293</v>
+        <v>45308.204799098799</v>
       </c>
       <c r="C13">
-        <v>6478.2838473706397</v>
+        <v>64528.204799098799</v>
       </c>
       <c r="D13">
-        <v>0.20576923076923001</v>
+        <v>0.163942307692307</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G13">
-        <v>1.3333333333333299</v>
+        <v>0</v>
       </c>
       <c r="M13" t="s">
         <v>24</v>
@@ -17871,22 +16729,22 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>4814.2922609916404</v>
+        <v>31585.367319657598</v>
       </c>
       <c r="C14">
-        <v>21454.292260991599</v>
+        <v>50305.367319657598</v>
       </c>
       <c r="D14">
-        <v>0.20897435897435801</v>
+        <v>0.16963141025640999</v>
       </c>
       <c r="E14">
-        <v>71</v>
+        <v>142</v>
       </c>
       <c r="F14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G14">
-        <v>8</v>
+        <v>4.75</v>
       </c>
       <c r="M14" t="s">
         <v>25</v>
@@ -17927,22 +16785,22 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>-773.16832511706798</v>
+        <v>16051.7500170203</v>
       </c>
       <c r="C15">
-        <v>17126.831674882898</v>
+        <v>33311.750017020298</v>
       </c>
       <c r="D15">
-        <v>0.19679487179487101</v>
+        <v>0.20121794871794799</v>
       </c>
       <c r="E15">
-        <v>55</v>
+        <v>118</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G15">
-        <v>5.25</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="M15" t="s">
         <v>26</v>
@@ -17965,22 +16823,22 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>827.52100349728005</v>
+        <v>28257.789059749201</v>
       </c>
       <c r="C16">
-        <v>17227.521003497201</v>
+        <v>46117.789059749201</v>
       </c>
       <c r="D16">
-        <v>0.298397435897435</v>
+        <v>0.17259615384615301</v>
       </c>
       <c r="E16">
-        <v>55</v>
+        <v>137</v>
       </c>
       <c r="F16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G16">
-        <v>8.625</v>
+        <v>5.4</v>
       </c>
       <c r="M16" t="s">
         <v>27</v>
@@ -18009,22 +16867,22 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>4697.4904012275301</v>
+        <v>6574.8033378974396</v>
       </c>
       <c r="C17">
-        <v>20297.4904012275</v>
+        <v>26414.8033378974</v>
       </c>
       <c r="D17">
-        <v>0.28717948717948699</v>
+        <v>0.13351648351648299</v>
       </c>
       <c r="E17">
-        <v>99</v>
+        <v>211</v>
       </c>
       <c r="F17">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G17">
-        <v>5.8</v>
+        <v>4.6666666666666599</v>
       </c>
       <c r="M17" t="s">
         <v>28</v>
@@ -18059,22 +16917,22 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>29093.424458147601</v>
+        <v>36900.947212065803</v>
       </c>
       <c r="C18">
-        <v>46153.424458147601</v>
+        <v>56180.947212065803</v>
       </c>
       <c r="D18">
-        <v>0.15544871794871701</v>
+        <v>0.193732193732193</v>
       </c>
       <c r="E18">
-        <v>140</v>
+        <v>225</v>
       </c>
       <c r="F18">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G18">
-        <v>3.9230769230769198</v>
+        <v>4.7333333333333298</v>
       </c>
       <c r="M18" t="s">
         <v>29</v>
@@ -18097,22 +16955,22 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>10872.766968525801</v>
+        <v>37195.753741472698</v>
       </c>
       <c r="C19">
-        <v>26072.766968525801</v>
+        <v>54775.753741472698</v>
       </c>
       <c r="D19">
-        <v>0.142788461538461</v>
+        <v>0.183760683760683</v>
       </c>
       <c r="E19">
-        <v>76</v>
+        <v>129</v>
       </c>
       <c r="F19">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G19">
-        <v>2.5</v>
+        <v>5.6666666666666599</v>
       </c>
       <c r="M19" t="s">
         <v>30</v>
@@ -18135,22 +16993,22 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>1932.6281178905001</v>
+        <v>12370.7033507903</v>
       </c>
       <c r="C20">
-        <v>18732.628117890501</v>
+        <v>30010.7033507903</v>
       </c>
       <c r="D20">
-        <v>0.135897435897435</v>
+        <v>0.18647435897435799</v>
       </c>
       <c r="E20">
-        <v>25</v>
+        <v>147</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>5.625</v>
       </c>
       <c r="M20" t="s">
         <v>31</v>
@@ -18191,22 +17049,22 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>-2892.6446816621201</v>
+        <v>29005.404307938399</v>
       </c>
       <c r="C21">
-        <v>15407.355318337801</v>
+        <v>48965.404307938399</v>
       </c>
       <c r="D21">
-        <v>0.15982905982905901</v>
+        <v>0.19109686609686599</v>
       </c>
       <c r="E21">
-        <v>58</v>
+        <v>335</v>
       </c>
       <c r="F21">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G21">
-        <v>7.5</v>
+        <v>2.4666666666666601</v>
       </c>
       <c r="M21" t="s">
         <v>32</v>
@@ -18249,31 +17107,31 @@
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B23">
         <f>AVERAGE(B2:B21)</f>
-        <v>650.80750864870913</v>
+        <v>25728.222001338563</v>
       </c>
       <c r="C23">
         <f t="shared" ref="C23:G23" si="0">AVERAGE(C2:C21)</f>
-        <v>17551.807508648668</v>
+        <v>44280.222001338559</v>
       </c>
       <c r="D23">
         <f t="shared" si="0"/>
-        <v>0.17206597222222167</v>
+        <v>0.17233147003459445</v>
       </c>
       <c r="E23">
         <f t="shared" si="0"/>
-        <v>66.2</v>
+        <v>168.75</v>
       </c>
       <c r="F23">
         <f t="shared" si="0"/>
-        <v>5.2</v>
+        <v>11.1</v>
       </c>
       <c r="G23">
         <f t="shared" si="0"/>
-        <v>4.6561538461538454</v>
+        <v>3.5858351370851329</v>
       </c>
       <c r="M23" t="s">
         <v>34</v>
@@ -18305,31 +17163,31 @@
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B24">
         <f>_xlfn.STDEV.S(B2:B21)</f>
-        <v>8676.4816826054102</v>
+        <v>10033.370106107655</v>
       </c>
       <c r="C24">
         <f t="shared" ref="C24:G24" si="1">_xlfn.STDEV.S(C2:C21)</f>
-        <v>8469.5875230645815</v>
+        <v>10239.971137545737</v>
       </c>
       <c r="D24">
         <f t="shared" si="1"/>
-        <v>5.1717053139296025E-2</v>
+        <v>1.9210076924795757E-2</v>
       </c>
       <c r="E24">
         <f t="shared" si="1"/>
-        <v>48.088295982768152</v>
+        <v>55.974500773496011</v>
       </c>
       <c r="F24">
         <f t="shared" si="1"/>
-        <v>2.6477398504742635</v>
+        <v>2.0493901531919221</v>
       </c>
       <c r="G24">
         <f t="shared" si="1"/>
-        <v>3.5613710382033137</v>
+        <v>2.2144854241143319</v>
       </c>
       <c r="M24" t="s">
         <v>35</v>
@@ -18533,7 +17391,7 @@
         <v>22</v>
       </c>
       <c r="AB33" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34" spans="13:28" x14ac:dyDescent="0.35">
@@ -18583,7 +17441,7 @@
         <v>22</v>
       </c>
       <c r="AB34" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35" spans="13:28" x14ac:dyDescent="0.35">
@@ -18633,7 +17491,7 @@
         <v>22</v>
       </c>
       <c r="AB35" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36" spans="13:28" x14ac:dyDescent="0.35">
@@ -18659,7 +17517,7 @@
         <v>46</v>
       </c>
       <c r="T36" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="U36" t="s">
         <v>22</v>
@@ -18683,7 +17541,7 @@
         <v>22</v>
       </c>
       <c r="AB36" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37" spans="13:28" x14ac:dyDescent="0.35">
@@ -18733,7 +17591,7 @@
         <v>22</v>
       </c>
       <c r="AB37" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38" spans="13:28" x14ac:dyDescent="0.35">
@@ -18783,7 +17641,7 @@
         <v>22</v>
       </c>
       <c r="AB38" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39" spans="13:28" x14ac:dyDescent="0.35">
@@ -18833,7 +17691,7 @@
         <v>22</v>
       </c>
       <c r="AB39" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="13:28" x14ac:dyDescent="0.35">
@@ -18883,7 +17741,7 @@
         <v>22</v>
       </c>
       <c r="AB40" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41" spans="13:28" x14ac:dyDescent="0.35">
@@ -18933,7 +17791,7 @@
         <v>22</v>
       </c>
       <c r="AB41" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
     </row>
     <row r="42" spans="13:28" x14ac:dyDescent="0.35">
@@ -18983,7 +17841,7 @@
         <v>22</v>
       </c>
       <c r="AB42" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="43" spans="13:28" x14ac:dyDescent="0.35">
@@ -19033,7 +17891,7 @@
         <v>22</v>
       </c>
       <c r="AB43" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="44" spans="13:28" x14ac:dyDescent="0.35">
@@ -19083,7 +17941,7 @@
         <v>22</v>
       </c>
       <c r="AB44" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="45" spans="13:28" x14ac:dyDescent="0.35">
@@ -19109,7 +17967,7 @@
         <v>46</v>
       </c>
       <c r="T45" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="U45" t="s">
         <v>22</v>
@@ -19133,7 +17991,7 @@
         <v>22</v>
       </c>
       <c r="AB45" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="46" spans="13:28" x14ac:dyDescent="0.35">
@@ -20784,7 +19642,7 @@
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B23">
         <f>AVERAGE(B2:B21)</f>
@@ -20828,7 +19686,7 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B24">
         <f>_xlfn.STDEV.S(B2:B21)</f>
@@ -21032,7 +19890,7 @@
         <v>22</v>
       </c>
       <c r="AB33" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="34" spans="13:28" x14ac:dyDescent="0.35">
@@ -21082,7 +19940,7 @@
         <v>22</v>
       </c>
       <c r="AB34" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
     </row>
     <row r="35" spans="13:28" x14ac:dyDescent="0.35">
@@ -21132,7 +19990,7 @@
         <v>22</v>
       </c>
       <c r="AB35" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
     </row>
     <row r="36" spans="13:28" x14ac:dyDescent="0.35">
@@ -22110,7 +20968,7 @@
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B23">
         <f>AVERAGE(B2:B21)</f>
@@ -22154,7 +21012,7 @@
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B24">
         <f>_xlfn.STDEV.S(B2:B21)</f>
@@ -22369,7 +21227,7 @@
         <v>46</v>
       </c>
       <c r="U34" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="V34" t="s">
         <v>22</v>
@@ -22393,7 +21251,7 @@
         <v>22</v>
       </c>
       <c r="AC34" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35" spans="14:29" x14ac:dyDescent="0.35">
@@ -22419,7 +21277,7 @@
         <v>46</v>
       </c>
       <c r="U35" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="V35" t="s">
         <v>22</v>
@@ -22443,7 +21301,7 @@
         <v>22</v>
       </c>
       <c r="AC35" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="36" spans="14:29" x14ac:dyDescent="0.35">
@@ -22493,7 +21351,7 @@
         <v>22</v>
       </c>
       <c r="AC36" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37" spans="14:29" x14ac:dyDescent="0.35">
@@ -22543,7 +21401,7 @@
         <v>22</v>
       </c>
       <c r="AC37" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="38" spans="14:29" x14ac:dyDescent="0.35">
@@ -22593,7 +21451,7 @@
         <v>22</v>
       </c>
       <c r="AC38" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="39" spans="14:29" x14ac:dyDescent="0.35">
@@ -22619,7 +21477,7 @@
         <v>46</v>
       </c>
       <c r="U39" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="V39" t="s">
         <v>22</v>
@@ -22643,7 +21501,7 @@
         <v>22</v>
       </c>
       <c r="AC39" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="40" spans="14:29" x14ac:dyDescent="0.35">
@@ -22693,7 +21551,7 @@
         <v>22</v>
       </c>
       <c r="AC40" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
     </row>
     <row r="41" spans="14:29" x14ac:dyDescent="0.35">
@@ -22743,7 +21601,7 @@
         <v>22</v>
       </c>
       <c r="AC41" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
     </row>
     <row r="42" spans="14:29" x14ac:dyDescent="0.35">
@@ -22793,7 +21651,7 @@
         <v>22</v>
       </c>
       <c r="AC42" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="43" spans="14:29" x14ac:dyDescent="0.35">
@@ -22843,7 +21701,7 @@
         <v>22</v>
       </c>
       <c r="AC43" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
     </row>
     <row r="44" spans="14:29" x14ac:dyDescent="0.35">
@@ -22893,7 +21751,7 @@
         <v>22</v>
       </c>
       <c r="AC44" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="45" spans="14:29" x14ac:dyDescent="0.35">
@@ -22943,7 +21801,7 @@
         <v>22</v>
       </c>
       <c r="AC45" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46" spans="14:29" x14ac:dyDescent="0.35">
@@ -22993,7 +21851,7 @@
         <v>22</v>
       </c>
       <c r="AC46" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="47" spans="14:29" x14ac:dyDescent="0.35">
